--- a/redis/redis_mapping.xlsx
+++ b/redis/redis_mapping.xlsx
@@ -1,15 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="132" yWindow="600" windowWidth="22716" windowHeight="10788"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jKlJ0PhOIio6kvxEmoeK2vVTScGS/xIveXy7SubI2Sk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="wTY03MNrtljB1BJALhKZeaeU1gms4Oh8Xh4CIERQ3w8="/>
     </ext>
   </extLst>
 </workbook>
@@ -711,10 +714,10 @@
     <t>BUYER_STATUS</t>
   </si>
   <si>
-    <t>trolley_status</t>
-  </si>
-  <si>
-    <t>TROLLEY_STATUS</t>
+    <t>trolley_remark</t>
+  </si>
+  <si>
+    <t>TROLLEY_REMARK</t>
   </si>
   <si>
     <t>TROLLEY_DATE</t>
@@ -723,33 +726,35 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -757,7 +762,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -827,7 +832,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -841,82 +852,63 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="6" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="7" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1106,24 +1098,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:E191"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.14"/>
-    <col customWidth="1" min="2" max="2" width="22.71"/>
-    <col customWidth="1" min="3" max="3" width="27.0"/>
-    <col customWidth="1" min="4" max="4" width="36.71"/>
-    <col customWidth="1" min="5" max="5" width="20.71"/>
+    <col min="1" max="1" width="27.109375" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1140,7 +1135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1157,7 +1152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1174,7 +1169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,7 +1186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1208,7 +1203,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1225,7 +1220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1242,7 +1237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1259,7 +1254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1276,7 +1271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1293,7 +1288,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
@@ -1310,7 +1305,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1327,7 +1322,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
@@ -1344,7 +1339,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1361,7 +1356,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1378,7 +1373,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
@@ -1395,7 +1390,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
@@ -1412,7 +1407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
@@ -1429,7 +1424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
@@ -1446,7 +1441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
@@ -1463,7 +1458,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
@@ -1480,7 +1475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
@@ -1497,7 +1492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>41</v>
       </c>
@@ -1514,7 +1509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>41</v>
       </c>
@@ -1531,7 +1526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>41</v>
       </c>
@@ -1548,7 +1543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>41</v>
       </c>
@@ -1565,7 +1560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>41</v>
       </c>
@@ -1582,7 +1577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>41</v>
       </c>
@@ -1599,7 +1594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
@@ -1616,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
@@ -1633,7 +1628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>41</v>
       </c>
@@ -1650,7 +1645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>41</v>
       </c>
@@ -1667,7 +1662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>41</v>
       </c>
@@ -1684,7 +1679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>41</v>
       </c>
@@ -1701,7 +1696,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>41</v>
       </c>
@@ -1718,7 +1713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>41</v>
       </c>
@@ -1735,7 +1730,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>41</v>
       </c>
@@ -1752,7 +1747,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>41</v>
       </c>
@@ -1769,7 +1764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
@@ -1786,7 +1781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
@@ -1803,7 +1798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>41</v>
       </c>
@@ -1820,7 +1815,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>69</v>
       </c>
@@ -1837,7 +1832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>69</v>
       </c>
@@ -1854,7 +1849,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>69</v>
       </c>
@@ -1871,7 +1866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>69</v>
       </c>
@@ -1888,7 +1883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>69</v>
       </c>
@@ -1905,7 +1900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>69</v>
       </c>
@@ -1922,7 +1917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>69</v>
       </c>
@@ -1939,7 +1934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>69</v>
       </c>
@@ -1956,7 +1951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>69</v>
       </c>
@@ -1973,7 +1968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>69</v>
       </c>
@@ -1990,7 +1985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>69</v>
       </c>
@@ -2007,7 +2002,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>69</v>
       </c>
@@ -2024,7 +2019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>69</v>
       </c>
@@ -2041,7 +2036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>69</v>
       </c>
@@ -2058,7 +2053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>69</v>
       </c>
@@ -2075,7 +2070,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>69</v>
       </c>
@@ -2092,7 +2087,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>69</v>
       </c>
@@ -2109,7 +2104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>69</v>
       </c>
@@ -2126,7 +2121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>69</v>
       </c>
@@ -2143,7 +2138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>69</v>
       </c>
@@ -2160,7 +2155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>69</v>
       </c>
@@ -2177,7 +2172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>69</v>
       </c>
@@ -2194,7 +2189,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>69</v>
       </c>
@@ -2211,7 +2206,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>69</v>
       </c>
@@ -2228,7 +2223,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>69</v>
       </c>
@@ -2245,7 +2240,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>69</v>
       </c>
@@ -2262,7 +2257,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>69</v>
       </c>
@@ -2279,7 +2274,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>69</v>
       </c>
@@ -2296,7 +2291,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
         <v>69</v>
       </c>
@@ -2313,7 +2308,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
         <v>69</v>
       </c>
@@ -2330,7 +2325,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>69</v>
       </c>
@@ -2347,7 +2342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>104</v>
       </c>
@@ -2364,7 +2359,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
         <v>104</v>
       </c>
@@ -2381,7 +2376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
         <v>104</v>
       </c>
@@ -2398,7 +2393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
         <v>104</v>
       </c>
@@ -2415,7 +2410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
         <v>104</v>
       </c>
@@ -2432,7 +2427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
         <v>104</v>
       </c>
@@ -2449,7 +2444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
         <v>104</v>
       </c>
@@ -2466,7 +2461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
         <v>104</v>
       </c>
@@ -2483,7 +2478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
         <v>104</v>
       </c>
@@ -2500,7 +2495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
         <v>104</v>
       </c>
@@ -2517,7 +2512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
         <v>104</v>
       </c>
@@ -2534,7 +2529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>104</v>
       </c>
@@ -2551,7 +2546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
         <v>104</v>
       </c>
@@ -2568,7 +2563,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="11" t="s">
         <v>104</v>
       </c>
@@ -2585,7 +2580,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="11" t="s">
         <v>104</v>
       </c>
@@ -2602,7 +2597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="11" t="s">
         <v>104</v>
       </c>
@@ -2619,7 +2614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="11" t="s">
         <v>104</v>
       </c>
@@ -2636,7 +2631,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="11" t="s">
         <v>104</v>
       </c>
@@ -2653,7 +2648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
         <v>104</v>
       </c>
@@ -2670,7 +2665,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
         <v>104</v>
       </c>
@@ -2687,7 +2682,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
         <v>104</v>
       </c>
@@ -2704,7 +2699,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
         <v>104</v>
       </c>
@@ -2721,7 +2716,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="11" t="s">
         <v>104</v>
       </c>
@@ -2738,7 +2733,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="11" t="s">
         <v>104</v>
       </c>
@@ -2755,7 +2750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
         <v>104</v>
       </c>
@@ -2772,7 +2767,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="11" t="s">
         <v>104</v>
       </c>
@@ -2789,7 +2784,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="11" t="s">
         <v>104</v>
       </c>
@@ -2806,7 +2801,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="11" t="s">
         <v>104</v>
       </c>
@@ -2823,7 +2818,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
         <v>104</v>
       </c>
@@ -2840,7 +2835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
         <v>133</v>
       </c>
@@ -2857,7 +2852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" s="14" t="s">
         <v>133</v>
       </c>
@@ -2874,7 +2869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A104" s="14" t="s">
         <v>133</v>
       </c>
@@ -2891,7 +2886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" s="14" t="s">
         <v>133</v>
       </c>
@@ -2908,7 +2903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
         <v>133</v>
       </c>
@@ -2925,7 +2920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A107" s="14" t="s">
         <v>133</v>
       </c>
@@ -2942,7 +2937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
         <v>133</v>
       </c>
@@ -2959,7 +2954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" s="14" t="s">
         <v>133</v>
       </c>
@@ -2976,7 +2971,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
         <v>133</v>
       </c>
@@ -2993,7 +2988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A111" s="14" t="s">
         <v>133</v>
       </c>
@@ -3010,14 +3005,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="15" t="s">
         <v>154</v>
       </c>
       <c r="D112" s="14" t="s">
@@ -3027,14 +3022,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A113" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="15" t="s">
         <v>156</v>
       </c>
       <c r="D113" s="14" t="s">
@@ -3044,7 +3039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A114" s="14" t="s">
         <v>133</v>
       </c>
@@ -3061,7 +3056,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A115" s="14" t="s">
         <v>133</v>
       </c>
@@ -3078,7 +3073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A116" s="14" t="s">
         <v>133</v>
       </c>
@@ -3095,7 +3090,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A117" s="14" t="s">
         <v>133</v>
       </c>
@@ -3112,7 +3107,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A118" s="14" t="s">
         <v>133</v>
       </c>
@@ -3129,7 +3124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A119" s="14" t="s">
         <v>133</v>
       </c>
@@ -3146,7 +3141,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A120" s="14" t="s">
         <v>133</v>
       </c>
@@ -3163,1214 +3158,1214 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="15" t="s">
+    <row r="121" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A121" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B121" s="15" t="s">
+      <c r="B121" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="C121" s="15" t="s">
+      <c r="C121" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D121" s="15" t="s">
+      <c r="D121" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E121" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="s">
+      <c r="E121" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A122" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C122" s="15" t="s">
+      <c r="C122" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="D122" s="15" t="s">
+      <c r="D122" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E122" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="s">
+      <c r="E122" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A123" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="C123" s="15" t="s">
+      <c r="C123" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D123" s="15" t="s">
+      <c r="D123" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E123" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="15" t="s">
+      <c r="E123" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A124" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B124" s="15" t="s">
+      <c r="B124" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D124" s="15" t="s">
+      <c r="D124" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E124" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="15" t="s">
+      <c r="E124" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A125" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B125" s="15" t="s">
+      <c r="B125" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="C125" s="15" t="s">
+      <c r="C125" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="D125" s="15" t="s">
+      <c r="D125" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E125" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="15" t="s">
+      <c r="E125" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A126" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B126" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C126" s="15" t="s">
+      <c r="C126" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="D126" s="15" t="s">
+      <c r="D126" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E126" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="15" t="s">
+      <c r="E126" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A127" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C127" s="15" t="s">
+      <c r="C127" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D127" s="15" t="s">
+      <c r="D127" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E127" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="15" t="s">
+      <c r="E127" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A128" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B128" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="C128" s="15" t="s">
+      <c r="C128" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="D128" s="15" t="s">
+      <c r="D128" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E128" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="15" t="s">
+      <c r="E128" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A129" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B129" s="15" t="s">
+      <c r="B129" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="C129" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D129" s="15" t="s">
+      <c r="D129" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E129" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="15" t="s">
+      <c r="E129" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A130" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B130" s="15" t="s">
+      <c r="B130" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C130" s="15" t="s">
+      <c r="C130" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D130" s="15" t="s">
+      <c r="D130" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E130" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="15" t="s">
+      <c r="E130" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A131" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="D131" s="15" t="s">
+      <c r="D131" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E131" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="15" t="s">
+      <c r="E131" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A132" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B132" s="15" t="s">
+      <c r="B132" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C132" s="15" t="s">
+      <c r="C132" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D132" s="15" t="s">
+      <c r="D132" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E132" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="15" t="s">
+      <c r="E132" s="16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A133" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B133" s="15" t="s">
+      <c r="B133" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C133" s="15" t="s">
+      <c r="C133" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="D133" s="15" t="s">
+      <c r="D133" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E133" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="s">
+      <c r="E133" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A134" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B134" s="15" t="s">
+      <c r="B134" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C134" s="15" t="s">
+      <c r="C134" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D134" s="15" t="s">
+      <c r="D134" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E134" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="15" t="s">
+      <c r="E134" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A135" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B135" s="15" t="s">
+      <c r="B135" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="C135" s="15" t="s">
+      <c r="C135" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D135" s="15" t="s">
+      <c r="D135" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E135" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="s">
+      <c r="E135" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A136" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B136" s="15" t="s">
+      <c r="B136" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C136" s="15" t="s">
+      <c r="C136" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D136" s="15" t="s">
+      <c r="D136" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E136" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="15" t="s">
+      <c r="E136" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A137" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B137" s="15" t="s">
+      <c r="B137" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C137" s="15" t="s">
+      <c r="C137" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D137" s="15" t="s">
+      <c r="D137" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E137" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="s">
+      <c r="E137" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A138" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B138" s="15" t="s">
+      <c r="B138" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C138" s="15" t="s">
+      <c r="C138" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D138" s="15" t="s">
+      <c r="D138" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E138" s="15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="16" t="s">
+      <c r="E138" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A139" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B139" s="16" t="s">
+      <c r="B139" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C139" s="16" t="s">
+      <c r="C139" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D139" s="16" t="s">
+      <c r="D139" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E139" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="16" t="s">
+      <c r="E139" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A140" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C140" s="16" t="s">
+      <c r="C140" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D140" s="16" t="s">
+      <c r="D140" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E140" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="16" t="s">
+      <c r="E140" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A141" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B141" s="16" t="s">
+      <c r="B141" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C141" s="16" t="s">
+      <c r="C141" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D141" s="16" t="s">
+      <c r="D141" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E141" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="16" t="s">
+      <c r="E141" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A142" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C142" s="16" t="s">
+      <c r="C142" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D142" s="16" t="s">
+      <c r="D142" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E142" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="16" t="s">
+      <c r="E142" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A143" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B143" s="16" t="s">
+      <c r="B143" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C143" s="16" t="s">
+      <c r="C143" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D143" s="16" t="s">
+      <c r="D143" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E143" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="16" t="s">
+      <c r="E143" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A144" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C144" s="16" t="s">
+      <c r="C144" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="D144" s="16" t="s">
+      <c r="D144" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E144" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="16" t="s">
+      <c r="E144" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A145" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B145" s="16" t="s">
+      <c r="B145" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C145" s="16" t="s">
+      <c r="C145" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="D145" s="16" t="s">
+      <c r="D145" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E145" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="16" t="s">
+      <c r="E145" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A146" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B146" s="16" t="s">
+      <c r="B146" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C146" s="16" t="s">
+      <c r="C146" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="D146" s="16" t="s">
+      <c r="D146" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E146" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="16" t="s">
+      <c r="E146" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A147" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B147" s="16" t="s">
+      <c r="B147" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C147" s="16" t="s">
+      <c r="C147" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D147" s="16" t="s">
+      <c r="D147" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E147" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="16" t="s">
+      <c r="E147" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A148" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B148" s="16" t="s">
+      <c r="B148" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C148" s="16" t="s">
+      <c r="C148" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="D148" s="16" t="s">
+      <c r="D148" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E148" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="16" t="s">
+      <c r="E148" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A149" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B149" s="16" t="s">
+      <c r="B149" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C149" s="16" t="s">
+      <c r="C149" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="D149" s="16" t="s">
+      <c r="D149" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E149" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="16" t="s">
+      <c r="E149" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A150" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C150" s="16" t="s">
+      <c r="C150" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D150" s="16" t="s">
+      <c r="D150" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E150" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="16" t="s">
+      <c r="E150" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A151" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C151" s="16" t="s">
+      <c r="C151" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D151" s="16" t="s">
+      <c r="D151" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E151" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="16" t="s">
+      <c r="E151" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A152" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C152" s="16" t="s">
+      <c r="C152" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D152" s="16" t="s">
+      <c r="D152" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E152" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="16" t="s">
+      <c r="E152" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A153" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C153" s="16" t="s">
+      <c r="C153" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="D153" s="16" t="s">
+      <c r="D153" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E153" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="16" t="s">
+      <c r="E153" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A154" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B154" s="16" t="s">
+      <c r="B154" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C154" s="16" t="s">
+      <c r="C154" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="D154" s="16" t="s">
+      <c r="D154" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E154" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="16" t="s">
+      <c r="E154" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A155" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B155" s="16" t="s">
+      <c r="B155" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C155" s="16" t="s">
+      <c r="C155" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="D155" s="16" t="s">
+      <c r="D155" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E155" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="s">
+      <c r="E155" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A156" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B156" s="16" t="s">
+      <c r="B156" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C156" s="16" t="s">
+      <c r="C156" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="D156" s="16" t="s">
+      <c r="D156" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E156" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="16" t="s">
+      <c r="E156" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A157" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B157" s="16" t="s">
+      <c r="B157" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C157" s="16" t="s">
+      <c r="C157" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="D157" s="16" t="s">
+      <c r="D157" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E157" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="16" t="s">
+      <c r="E157" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A158" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B158" s="16" t="s">
+      <c r="B158" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C158" s="16" t="s">
+      <c r="C158" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="D158" s="16" t="s">
+      <c r="D158" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E158" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="16" t="s">
+      <c r="E158" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A159" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B159" s="16" t="s">
+      <c r="B159" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C159" s="16" t="s">
+      <c r="C159" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="D159" s="16" t="s">
+      <c r="D159" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E159" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="16" t="s">
+      <c r="E159" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A160" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B160" s="16" t="s">
+      <c r="B160" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C160" s="16" t="s">
+      <c r="C160" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="D160" s="16" t="s">
+      <c r="D160" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="E160" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="161" ht="14.25" customHeight="1">
-      <c r="A161" s="17" t="s">
+      <c r="E160" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B161" s="17" t="s">
+      <c r="B161" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C161" s="17" t="s">
+      <c r="C161" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="D161" s="17" t="s">
+      <c r="D161" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E161" s="17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="17" t="s">
+      <c r="E161" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B162" s="17" t="s">
+      <c r="B162" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C162" s="17" t="s">
+      <c r="C162" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="D162" s="17" t="s">
+      <c r="D162" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E162" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="17" t="s">
+      <c r="E162" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B163" s="17" t="s">
+      <c r="B163" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C163" s="17" t="s">
+      <c r="C163" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="D163" s="17" t="s">
+      <c r="D163" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E163" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="164" ht="14.25" customHeight="1">
-      <c r="A164" s="17" t="s">
+      <c r="E163" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B164" s="17" t="s">
+      <c r="B164" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C164" s="17" t="s">
+      <c r="C164" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="D164" s="17" t="s">
+      <c r="D164" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E164" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="18" t="s">
+      <c r="E164" s="18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A165" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B165" s="18" t="s">
+      <c r="B165" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C165" s="18" t="s">
+      <c r="C165" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D165" s="18" t="s">
+      <c r="D165" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E165" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="18" t="s">
+      <c r="E165" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A166" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B166" s="18" t="s">
+      <c r="B166" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="C166" s="18" t="s">
+      <c r="C166" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="D166" s="18" t="s">
+      <c r="D166" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E166" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="18" t="s">
+      <c r="E166" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A167" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B167" s="18" t="s">
+      <c r="B167" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C167" s="18" t="s">
+      <c r="C167" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D167" s="18" t="s">
+      <c r="D167" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E167" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="18" t="s">
+      <c r="E167" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A168" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B168" s="18" t="s">
+      <c r="B168" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C168" s="18" t="s">
+      <c r="C168" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="D168" s="18" t="s">
+      <c r="D168" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E168" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="18" t="s">
+      <c r="E168" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A169" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B169" s="18" t="s">
+      <c r="B169" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="C169" s="18" t="s">
+      <c r="C169" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="D169" s="18" t="s">
+      <c r="D169" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E169" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="18" t="s">
+      <c r="E169" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A170" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B170" s="18" t="s">
+      <c r="B170" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C170" s="18" t="s">
+      <c r="C170" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="D170" s="18" t="s">
+      <c r="D170" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E170" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="18" t="s">
+      <c r="E170" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A171" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B171" s="18" t="s">
+      <c r="B171" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C171" s="18" t="s">
+      <c r="C171" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D171" s="18" t="s">
+      <c r="D171" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E171" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="18" t="s">
+      <c r="E171" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A172" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B172" s="18" t="s">
+      <c r="B172" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="C172" s="18" t="s">
+      <c r="C172" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="D172" s="18" t="s">
+      <c r="D172" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E172" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="18" t="s">
+      <c r="E172" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A173" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B173" s="18" t="s">
+      <c r="B173" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C173" s="18" t="s">
+      <c r="C173" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D173" s="18" t="s">
+      <c r="D173" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E173" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="18" t="s">
+      <c r="E173" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A174" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B174" s="18" t="s">
+      <c r="B174" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C174" s="18" t="s">
+      <c r="C174" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D174" s="18" t="s">
+      <c r="D174" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E174" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="18" t="s">
+      <c r="E174" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A175" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B175" s="18" t="s">
+      <c r="B175" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C175" s="18" t="s">
+      <c r="C175" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D175" s="18" t="s">
+      <c r="D175" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E175" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="18" t="s">
+      <c r="E175" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A176" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B176" s="18" t="s">
+      <c r="B176" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C176" s="18" t="s">
+      <c r="C176" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D176" s="18" t="s">
+      <c r="D176" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E176" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="18" t="s">
+      <c r="E176" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A177" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B177" s="18" t="s">
+      <c r="B177" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C177" s="18" t="s">
+      <c r="C177" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="D177" s="18" t="s">
+      <c r="D177" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E177" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="18" t="s">
+      <c r="E177" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A178" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B178" s="18" t="s">
+      <c r="B178" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C178" s="18" t="s">
+      <c r="C178" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="D178" s="18" t="s">
+      <c r="D178" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E178" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="18" t="s">
+      <c r="E178" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A179" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="B179" s="18" t="s">
+      <c r="B179" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C179" s="18" t="s">
+      <c r="C179" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="D179" s="18" t="s">
+      <c r="D179" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E179" s="18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="180" ht="14.25" customHeight="1">
-      <c r="A180" s="19" t="s">
+      <c r="E179" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="B180" s="19" t="s">
+      <c r="B180" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C180" s="19" t="s">
+      <c r="C180" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D180" s="19" t="s">
+      <c r="D180" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="E180" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="20" t="s">
+      <c r="E180" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A181" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B181" s="20" t="s">
+      <c r="B181" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C181" s="20" t="s">
+      <c r="C181" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="D181" s="20" t="s">
+      <c r="D181" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E181" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="20" t="s">
+      <c r="E181" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A182" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B182" s="20" t="s">
+      <c r="B182" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="C182" s="20" t="s">
+      <c r="C182" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="D182" s="20" t="s">
+      <c r="D182" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E182" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="20" t="s">
+      <c r="E182" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A183" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B183" s="20" t="s">
+      <c r="B183" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C183" s="20" t="s">
+      <c r="C183" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D183" s="20" t="s">
+      <c r="D183" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E183" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="20" t="s">
+      <c r="E183" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A184" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B184" s="20" t="s">
+      <c r="B184" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C184" s="20" t="s">
+      <c r="C184" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="D184" s="20" t="s">
+      <c r="D184" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E184" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="20" t="s">
+      <c r="E184" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A185" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B185" s="20" t="s">
+      <c r="B185" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C185" s="20" t="s">
+      <c r="C185" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D185" s="20" t="s">
+      <c r="D185" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E185" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="20" t="s">
+      <c r="E185" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A186" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B186" s="20" t="s">
+      <c r="B186" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C186" s="20" t="s">
+      <c r="C186" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D186" s="20" t="s">
+      <c r="D186" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E186" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="20" t="s">
+      <c r="E186" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A187" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B187" s="20" t="s">
+      <c r="B187" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C187" s="20" t="s">
+      <c r="C187" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D187" s="20" t="s">
+      <c r="D187" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E187" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="20" t="s">
+      <c r="E187" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A188" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B188" s="20" t="s">
+      <c r="B188" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="C188" s="20" t="s">
+      <c r="C188" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="D188" s="20" t="s">
+      <c r="D188" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E188" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="20" t="s">
+      <c r="E188" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A189" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B189" s="20" t="s">
+      <c r="B189" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C189" s="20" t="s">
+      <c r="C189" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="D189" s="20" t="s">
+      <c r="D189" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E189" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="190" ht="14.25" customHeight="1">
-      <c r="A190" s="21" t="s">
+      <c r="E189" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B190" s="21" t="s">
+      <c r="B190" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C190" s="21" t="s">
+      <c r="C190" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="D190" s="21" t="s">
+      <c r="D190" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E190" s="21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="191" ht="14.25" customHeight="1">
-      <c r="A191" s="21" t="s">
+      <c r="E190" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="B191" s="21" t="s">
+      <c r="B191" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C191" s="21" t="s">
+      <c r="C191" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="D191" s="21" t="s">
+      <c r="D191" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="E191" s="21" t="s">
+      <c r="E191" s="22" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>